--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Diritti di rogito.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Diritti di rogito.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="115">
   <si>
     <r>
       <t xml:space="preserve">
@@ -777,7 +777,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">  firmato il </t>
+      <t xml:space="preserve"> firmato il </t>
     </r>
     <r>
       <rPr>
@@ -904,7 +904,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t>[Solo per messaggi Premium con allegato]</t>
+      <t>[Solo per messaggi con allegato]</t>
     </r>
     <r>
       <rPr>
@@ -1166,7 +1166,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1260,26 +1260,8 @@
     </r>
   </si>
   <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mancato pagamento
 Il seguente messaggio serve a sollecitare il cittadino per il mancato pagamento ma non costituisce in alcun modo un avviso a valore legale (i.e. notifica).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firma con IO
-Tramite la funzionalità Firma con IO puoi inviare al destinatario il documento da firmare e permettere la firma direttamente in app. Scopri di più (https://firma.io.italia.it/)
-Il seguente messaggio è da utilizzare nei casi di altre modalità di firma e non è necessario quando si utilizza Firma con IO.
-✨ Allegati Premium — Tramite questa funzionalità Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, puoi allegare documenti all'interno del messaggio.
-Questo messaggio è da utilizzare sia per messaggi Premium, sia per messaggi standard. In caso di messaggio standard, ricorda di eliminare ogni riferimento agli allegati dal corpo del messaggio.</t>
-  </si>
-  <si>
-    <t>✨Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi dell'appuntamento tramite notifica push.</t>
   </si>
 </sst>
 </file>
@@ -2146,22 +2128,22 @@
         <v>58</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F11" s="34" t="s">
         <v>58</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="I11" s="34" t="s">
         <v>58</v>
